--- a/results/class_sensitivity/recurrence_vs_global_drug_sensitivity.xlsx
+++ b/results/class_sensitivity/recurrence_vs_global_drug_sensitivity.xlsx
@@ -771,7 +771,7 @@
         <v>-0.1783653544666676</v>
       </c>
       <c r="C19" t="n">
-        <v>0.6511627906976745</v>
+        <v>0.6525044722719142</v>
       </c>
     </row>
     <row r="20">
@@ -888,7 +888,7 @@
         <v>-0.2539667075870732</v>
       </c>
       <c r="C28" t="n">
-        <v>0.462962962962963</v>
+        <v>0.4642857142857143</v>
       </c>
     </row>
     <row r="29">
@@ -927,7 +927,7 @@
         <v>-0.1998464016445489</v>
       </c>
       <c r="C31" t="n">
-        <v>0.3908730158730159</v>
+        <v>0.3888888888888889</v>
       </c>
     </row>
     <row r="32">
@@ -992,7 +992,7 @@
         <v>-0.226134911817538</v>
       </c>
       <c r="C36" t="n">
-        <v>0.9285714285714286</v>
+        <v>0.9259259259259259</v>
       </c>
     </row>
     <row r="37">
@@ -1005,7 +1005,7 @@
         <v>-0.222738672149269</v>
       </c>
       <c r="C37" t="n">
-        <v>0.3232142857142857</v>
+        <v>0.325</v>
       </c>
     </row>
     <row r="38">
@@ -1083,7 +1083,7 @@
         <v>-0.2246998597349494</v>
       </c>
       <c r="C43" t="n">
-        <v>0.7113095238095238</v>
+        <v>0.7083333333333334</v>
       </c>
     </row>
     <row r="44">

--- a/results/class_sensitivity/recurrence_vs_global_drug_sensitivity.xlsx
+++ b/results/class_sensitivity/recurrence_vs_global_drug_sensitivity.xlsx
@@ -641,7 +641,7 @@
         <v>-0.1662653967408163</v>
       </c>
       <c r="C9" t="n">
-        <v>0.5172413793103449</v>
+        <v>0.5144346431435445</v>
       </c>
     </row>
     <row r="10">
@@ -771,7 +771,7 @@
         <v>-0.1783653544666676</v>
       </c>
       <c r="C19" t="n">
-        <v>0.6525044722719142</v>
+        <v>0.6470099667774087</v>
       </c>
     </row>
     <row r="20">
@@ -888,7 +888,7 @@
         <v>-0.2539667075870732</v>
       </c>
       <c r="C28" t="n">
-        <v>0.4642857142857143</v>
+        <v>0.4636243386243386</v>
       </c>
     </row>
     <row r="29">
@@ -992,7 +992,7 @@
         <v>-0.226134911817538</v>
       </c>
       <c r="C36" t="n">
-        <v>0.9259259259259259</v>
+        <v>0.9285714285714286</v>
       </c>
     </row>
     <row r="37">
@@ -1005,7 +1005,7 @@
         <v>-0.222738672149269</v>
       </c>
       <c r="C37" t="n">
-        <v>0.325</v>
+        <v>0.3214285714285715</v>
       </c>
     </row>
     <row r="38">
